--- a/Outputs/Scenarios/PtX_demand_HR_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_HR_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0006628818471006026</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00142970240023261</v>
+        <v>0.0008147123759139894</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0004765674667442035</v>
+        <v>0.001097687470464919</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>9.55100534594075e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0004765674667442035</v>
+        <v>0.0004704374873421084</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.000981315871154448</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00768989981675487</v>
+        <v>0.004382070386976756</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.00256329993891829</v>
+        <v>0.005904100515330285</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>5.164820374497096e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.00256329993891829</v>
+        <v>0.002530328792284408</v>
       </c>
     </row>
     <row r="43">
